--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="G2" s="21">
         <f>B3+G1*7</f>
-        <v>280</v>
+        <v>46137</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>80000</v>
+        <v>76000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -862,9 +862,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>45857</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -888,9 +894,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45864</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>76000</v>
+        <v>72000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -926,9 +926,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45876</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -952,9 +958,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45880</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>72000</v>
+        <v>68000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -990,9 +990,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45884</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1016,9 +1022,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12000</v>
+        <v>22000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>68000</v>
+        <v>58000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1054,9 +1054,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1080,9 +1086,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1106,9 +1118,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45914</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1132,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45921</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1158,9 +1182,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45928</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>22000</v>
+        <v>26000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>58000</v>
+        <v>54000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1214,9 +1214,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45933</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1240,9 +1246,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45933</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>26000</v>
+        <v>34000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>54000</v>
+        <v>46000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1278,9 +1278,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45959</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1304,9 +1310,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45961</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1330,9 +1342,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45966</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1356,9 +1374,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45975</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>46000</v>
+        <v>44000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1406,9 +1406,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>36000</v>
+        <v>40000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>44000</v>
+        <v>40000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1438,9 +1438,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1464,9 +1470,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1502,9 +1502,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>46005</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>

--- a/LoanOfficer-A/2023/125 priya weekly.xlsx
+++ b/LoanOfficer-A/2023/125 priya weekly.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD20000.18-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>42000</v>
+        <v>46000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>38000</v>
+        <v>34000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1534,9 +1534,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1560,9 +1566,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
